--- a/SuppXLS/Scen_DemProj_DTCAR.xlsx
+++ b/SuppXLS/Scen_DemProj_DTCAR.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93AF0EE-2DFA-4600-BBC9-56DC63E60ECE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="BY_Data" sheetId="6" r:id="rId1"/>
-    <sheet name="CAR_Dem" sheetId="2" r:id="rId2"/>
+    <sheet name="BY_Data" sheetId="6" r:id="rId3"/>
+    <sheet name="CAR_Dem" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,7 +28,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
@@ -40,7 +40,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -119,13 +118,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -148,13 +153,8 @@
     <font>
       <b/>
       <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -167,13 +167,6 @@
       <color indexed="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -199,6 +192,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="43"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -217,19 +216,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF64C8FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -246,79 +239,208 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+  <cellStyleXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="24">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="24" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="24" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
-    <cellStyle name="40% - Accent3" xfId="1" builtinId="39"/>
-    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+  <cellStyles count="24">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 4 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normal 8" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normal 9 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normale_B2020" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Percent 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Percent 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Percent 3 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Percent 4" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Percent 4 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Percent 5" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Percent 6" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="40% - Accent3" xfId="20" builtinId="39"/>
+    <cellStyle name="Comma 2" xfId="21"/>
+    <cellStyle name="Normal 10" xfId="22"/>
+    <cellStyle name="Normal 2" xfId="23"/>
+    <cellStyle name="Normal 3" xfId="24"/>
+    <cellStyle name="Normal 4" xfId="25"/>
+    <cellStyle name="Normal 4 2" xfId="26"/>
+    <cellStyle name="Normal 8" xfId="27"/>
+    <cellStyle name="Normal 9 2" xfId="28"/>
+    <cellStyle name="Normale_B2020" xfId="29"/>
+    <cellStyle name="Percent 2" xfId="30"/>
+    <cellStyle name="Percent 3" xfId="31"/>
+    <cellStyle name="Percent 3 2" xfId="32"/>
+    <cellStyle name="Percent 4" xfId="33"/>
+    <cellStyle name="Percent 4 2" xfId="34"/>
+    <cellStyle name="Percent 5" xfId="35"/>
+    <cellStyle name="Percent 6" xfId="36"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="37"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -331,7 +453,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -345,12 +467,12 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{590892CD-39FE-4F52-AD6A-B78A6049AE07}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{590892cd-39fe-4f52-ad6a-b78a6049ae07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -358,12 +480,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1714500"/>
-          <a:ext cx="6918960" cy="590550"/>
+          <a:off x="609600" y="1724025"/>
+          <a:ext cx="4876800" cy="590550"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -372,7 +492,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -380,16 +500,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -400,7 +520,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -412,7 +532,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -423,7 +543,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -439,7 +559,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -453,12 +573,12 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>28574</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E90D4D9A-2272-4052-BC9F-7221AE552A28}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e90d4d9a-2272-4052-bc9f-7221ae552a28}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -466,12 +586,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="2295524"/>
+          <a:off x="609600" y="2295525"/>
           <a:ext cx="3619500" cy="600075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -480,7 +598,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -488,16 +606,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -508,7 +626,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -520,7 +638,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -531,7 +649,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -866,15 +984,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:J4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1428571428571" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
@@ -886,7 +1004,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="15.75" thickBot="1">
       <c r="B3" s="8" t="s">
         <v>13</v>
       </c>
@@ -915,7 +1033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" ht="15">
       <c r="B4" t="s">
         <v>15</v>
       </c>
@@ -940,31 +1058,31 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85714285714286" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="8.42857142857143" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="15">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -974,7 +1092,7 @@
       </c>
       <c r="L2" s="14"/>
     </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1003,7 +1121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:12" ht="15">
       <c r="D4" t="s">
         <v>9</v>
       </c>
@@ -1028,7 +1146,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:12" ht="15">
       <c r="D5" t="s">
         <v>9</v>
       </c>
@@ -1041,7 +1159,7 @@
       </c>
       <c r="G5" s="13">
         <f>BY_Data!$H$4*(1+$L$4)^(E5-2005)</f>
-        <v>3594.4416608362458</v>
+        <v>3594.4416608362467</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>10</v>
@@ -1049,7 +1167,7 @@
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:12" ht="15">
       <c r="D6" t="s">
         <v>9</v>
       </c>
@@ -1058,11 +1176,11 @@
       </c>
       <c r="F6" s="13">
         <f>BY_Data!$H$4*(1+$K$4)^(E6-2005)</f>
-        <v>3779.6103826455351</v>
+        <v>3779.610382645536</v>
       </c>
       <c r="G6" s="13">
         <f>BY_Data!$H$4*(1+$L$4)^(E6-2005)</f>
-        <v>4166.9430289912934</v>
+        <v>4166.9430289912953</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>10</v>
@@ -1070,7 +1188,7 @@
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:12" ht="15">
       <c r="D7" t="s">
         <v>9</v>
       </c>
@@ -1079,11 +1197,11 @@
       </c>
       <c r="F7" s="13">
         <f>BY_Data!$H$4*(1+$K$4)^(E7-2005)</f>
-        <v>4172.9952670543407</v>
+        <v>4172.9952670543425</v>
       </c>
       <c r="G7" s="13">
         <f>BY_Data!$H$4*(1+$L$4)^(E7-2005)</f>
-        <v>4830.6290225947205</v>
+        <v>4830.6290225947223</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>10</v>
@@ -1096,7 +1214,7 @@
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>